--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FB280E-6427-4C46-AA11-3D2292C108EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0FCB27-EFF7-4749-AE7E-C451615A9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>file</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>ted-mdb.1978</t>
+  </si>
+  <si>
+    <t>ted-mdb.2009</t>
+  </si>
+  <si>
+    <t>ted-mdb.2150</t>
   </si>
 </sst>
 </file>
@@ -396,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -447,7 +453,7 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E36" si="0">D3-C3</f>
+        <f t="shared" ref="E3:E41" si="0">D3-C3</f>
         <v>4.166666666666663E-2</v>
       </c>
     </row>
@@ -708,15 +714,33 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.64930555555555558</v>
+      </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.5972222222222276E-2</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.47222222222222221</v>
+      </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7361111111111105E-2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -731,26 +755,82 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E33" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F33" s="3">
+        <f>SUM(E29:E32)</f>
+        <v>3.3333333333333381E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.49652777777777779</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.51736111111111116</v>
+      </c>
       <c r="E34" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
+        <v>2.083333333333337E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C35" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.67847222222222225</v>
+      </c>
       <c r="E35" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.3">
+        <v>1.1805555555555625E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E36" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E37" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E38" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <f>SUM(E34:E38)</f>
+        <v>3.2638888888888995E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E39" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E40" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E41" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0FCB27-EFF7-4749-AE7E-C451615A9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A4662D-3908-4CD1-9514-AD6835593372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>file</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>ted-mdb.2150</t>
+  </si>
+  <si>
+    <t>abcnews.199762</t>
   </si>
 </sst>
 </file>
@@ -402,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -453,7 +456,7 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E41" si="0">D3-C3</f>
+        <f t="shared" ref="E3:E52" si="0">D3-C3</f>
         <v>4.166666666666663E-2</v>
       </c>
     </row>
@@ -497,9 +500,15 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
+      <c r="C7" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.55208333333333337</v>
+      </c>
       <c r="E7" s="3">
         <f>D7-C7</f>
-        <v>0</v>
+        <v>1.0416666666666741E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -515,7 +524,7 @@
       </c>
       <c r="F9" s="3">
         <f>SUM(E2:E9)</f>
-        <v>0.20138888888888873</v>
+        <v>0.21180555555555547</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -824,13 +833,91 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0.60069444444444442</v>
+      </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7361111111111049E-2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E41" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E42" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E43" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E44" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E45" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E46" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E47" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E48" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E49" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E50" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E51" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E52" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A4662D-3908-4CD1-9514-AD6835593372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B45662-7573-4086-A8AB-B916965F1745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>file</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>abcnews.199762</t>
+  </si>
+  <si>
+    <t>an-online.de.224441</t>
   </si>
 </sst>
 </file>
@@ -849,23 +852,44 @@
         <f t="shared" si="0"/>
         <v>1.7361111111111049E-2</v>
       </c>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E41" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F41" s="3">
+        <f>SUM(E40:E41)</f>
+        <v>1.7361111111111049E-2</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.80555555555555558</v>
+      </c>
       <c r="E42" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0416666666666741E-2</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E43" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <f>SUM(E42:E43)</f>
+        <v>1.0416666666666741E-2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B45662-7573-4086-A8AB-B916965F1745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CB417D-D28C-4DCB-BE5C-951D39462661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,13 +883,19 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C43" s="3">
+        <v>0.49652777777777779</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.50694444444444442</v>
+      </c>
       <c r="E43" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.041666666666663E-2</v>
       </c>
       <c r="F43" s="3">
         <f>SUM(E42:E43)</f>
-        <v>1.0416666666666741E-2</v>
+        <v>2.083333333333337E-2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CB417D-D28C-4DCB-BE5C-951D39462661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3476A4-7E17-4686-984B-886782054761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -459,7 +459,7 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E52" si="0">D3-C3</f>
+        <f t="shared" ref="E3:E54" si="0">D3-C3</f>
         <v>4.166666666666663E-2</v>
       </c>
     </row>
@@ -855,65 +855,76 @@
       <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C41" s="3">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="3">
-        <f>SUM(E40:E41)</f>
-        <v>1.7361111111111049E-2</v>
-      </c>
+        <v>6.9444444444445308E-3</v>
+      </c>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="E42" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E43" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <f>SUM(E40:E43)</f>
+        <v>2.430555555555558E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>15</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B44" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C44" s="3">
         <v>0.79513888888888884</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D44" s="3">
         <v>0.80555555555555558</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E44" s="3">
         <f t="shared" si="0"/>
         <v>1.0416666666666741E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C43" s="3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C45" s="3">
         <v>0.49652777777777779</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D45" s="3">
         <v>0.50694444444444442</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E45" s="3">
         <f t="shared" si="0"/>
         <v>1.041666666666663E-2</v>
       </c>
-      <c r="F43" s="3">
-        <f>SUM(E42:E43)</f>
-        <v>2.083333333333337E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E44" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E45" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C46" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0.59375</v>
+      </c>
       <c r="E46" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.041666666666663E-2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -927,6 +938,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="F48" s="3">
+        <f>SUM(E44:E48)</f>
+        <v>3.125E-2</v>
+      </c>
     </row>
     <row r="49" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E49" s="3">
@@ -948,6 +963,18 @@
     </row>
     <row r="52" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E52" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E53" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E54" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3476A4-7E17-4686-984B-886782054761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1153EE-A70C-439A-9FD1-69467E4E50F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="264" yWindow="1956" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>file</t>
   </si>
@@ -73,6 +73,15 @@
   </si>
   <si>
     <t>an-online.de.224441</t>
+  </si>
+  <si>
+    <t>ard.27823</t>
+  </si>
+  <si>
+    <t>augsburger-allgemeine.de.44740</t>
+  </si>
+  <si>
+    <t>bbc.242334</t>
   </si>
 </sst>
 </file>
@@ -408,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -459,7 +468,7 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E54" si="0">D3-C3</f>
+        <f t="shared" ref="E3:E63" si="0">D3-C3</f>
         <v>4.166666666666663E-2</v>
       </c>
     </row>
@@ -943,38 +952,148 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="3">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0.52777777777777779</v>
+      </c>
       <c r="E49" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.3">
+        <v>2.430555555555558E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C50" s="3">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="E50" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.3">
+        <v>6.9444444444445308E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E51" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F51" s="3">
+        <f>SUM(E49:E51)</f>
+        <v>3.1250000000000111E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0.7729166666666667</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.79374999999999996</v>
+      </c>
       <c r="E52" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.3">
+        <v>2.0833333333333259E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C53" s="3">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0.60763888888888884</v>
+      </c>
       <c r="E53" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.3">
+        <v>6.9444444444444198E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C54" s="3">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0.62847222222222221</v>
+      </c>
       <c r="E54" s="3">
+        <f t="shared" si="0"/>
+        <v>1.388888888888884E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E55" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="3">
+        <f>SUM(E52:E54)</f>
+        <v>4.1666666666666519E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E57" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E58" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E59" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E60" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E61" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E62" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E63" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1153EE-A70C-439A-9FD1-69467E4E50F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB213262-83AE-47A0-A5AE-8F1AE0A67C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="264" yWindow="1956" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1051,21 +1051,37 @@
       <c r="B56" t="s">
         <v>9</v>
       </c>
+      <c r="C56" s="3">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="E56" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.777777777777779E-2</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C57" s="3">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0.69791666666666663</v>
+      </c>
       <c r="E57" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.388888888888884E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E58" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <f>SUM(E56:E58)</f>
+        <v>4.166666666666663E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB213262-83AE-47A0-A5AE-8F1AE0A67C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE1B7BD-D87E-4E7A-BAE0-95ED32C08621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>file</t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>bbc.242334</t>
+  </si>
+  <si>
+    <t>bbc.242405</t>
+  </si>
+  <si>
+    <t>bbc.242418</t>
   </si>
 </sst>
 </file>
@@ -417,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -468,7 +474,7 @@
         <v>0.75</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E63" si="0">D3-C3</f>
+        <f t="shared" ref="E3:E66" si="0">D3-C3</f>
         <v>4.166666666666663E-2</v>
       </c>
     </row>
@@ -1075,13 +1081,19 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C58" s="3">
+        <v>0.67847222222222225</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.69930555555555551</v>
+      </c>
       <c r="E58" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.0833333333333259E-2</v>
       </c>
       <c r="F58" s="3">
         <f>SUM(E56:E58)</f>
-        <v>4.166666666666663E-2</v>
+        <v>6.2499999999999889E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -1091,26 +1103,144 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="3">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.71944444444444444</v>
+      </c>
       <c r="E60" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.1666666666666519E-3</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C61" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="E61" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.083333333333337E-2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C62" s="3">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="D62" s="3">
+        <v>0.625</v>
+      </c>
       <c r="E62" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.736111111111116E-2</v>
+      </c>
+      <c r="F62" s="3">
+        <f>SUM(E60:E62)</f>
+        <v>4.2361111111111183E-2</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E63" s="3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E65" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E66" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E67" s="3">
+        <f t="shared" ref="E67:E77" si="1">D67-C67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E68" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E69" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E70" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E71" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E72" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E73" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E74" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E75" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E76" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E77" s="3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE1B7BD-D87E-4E7A-BAE0-95ED32C08621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE95D66D-17AE-48B8-8351-82E948CC5C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14004" yWindow="0" windowWidth="9132" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
   <si>
     <t>file</t>
   </si>
@@ -88,6 +88,12 @@
   </si>
   <si>
     <t>bbc.242418</t>
+  </si>
+  <si>
+    <t>bbc.242436</t>
+  </si>
+  <si>
+    <t>bbc.242497</t>
   </si>
 </sst>
 </file>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1161,85 +1167,243 @@
       <c r="B64" t="s">
         <v>9</v>
       </c>
+      <c r="C64" s="3">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="D64" s="3">
+        <v>0.5625</v>
+      </c>
       <c r="E64" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.3">
+        <v>1.736111111111116E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C65" s="3">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D65" s="3">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="E65" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.3">
+        <v>1.0416666666666741E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C66" s="3">
+        <v>0.75555555555555554</v>
+      </c>
+      <c r="D66" s="3">
+        <v>0.75902777777777775</v>
+      </c>
       <c r="E66" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.3">
+        <v>3.4722222222222099E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E67" s="3">
-        <f t="shared" ref="E67:E77" si="1">D67-C67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.3">
+        <f t="shared" ref="E67:E95" si="1">D67-C67</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="3">
+        <f>SUM(E64:E67)</f>
+        <v>3.1250000000000111E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="3">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="E68" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.3">
+        <v>1.2499999999999956E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C69" s="3">
+        <v>0.73263888888888884</v>
+      </c>
+      <c r="D69" s="3">
+        <v>0.75347222222222221</v>
+      </c>
       <c r="E69" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.3">
+        <v>2.083333333333337E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E70" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E71" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F71" s="3">
+        <f>SUM(E68:E71)</f>
+        <v>3.3333333333333326E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
       <c r="E72" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E73" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E74" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E75" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E76" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E77" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E78" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E79" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E80" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E81" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E82" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E83" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E84" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E85" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E86" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E87" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E88" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E89" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E90" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E91" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E92" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E93" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E94" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E95" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE95D66D-17AE-48B8-8351-82E948CC5C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A502DAC0-10A1-4670-A64D-2467E719B3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14004" yWindow="0" windowWidth="9132" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>file</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>bbc.242497</t>
+  </si>
+  <si>
+    <t>braunschweiger-zeitung.de.48722</t>
+  </si>
+  <si>
+    <t>brisbanetimes.com.au.130272</t>
   </si>
 </sst>
 </file>
@@ -1265,9 +1271,15 @@
       <c r="B72" t="s">
         <v>9</v>
       </c>
+      <c r="C72" s="3">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D72" s="3">
+        <v>0.61527777777777781</v>
+      </c>
       <c r="E72" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2222222222222254E-2</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -1281,11 +1293,27 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="F74" s="3">
+        <f>SUM(E72:E74)</f>
+        <v>2.2222222222222254E-2</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75" s="3">
+        <v>0.65625</v>
+      </c>
+      <c r="D75" s="3">
+        <v>0.68263888888888891</v>
+      </c>
       <c r="E75" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.6388888888888906E-2</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -1299,8 +1327,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="F77" s="3">
+        <f>SUM(E75:E77)</f>
+        <v>2.6388888888888906E-2</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" t="s">
+        <v>9</v>
+      </c>
       <c r="E78" s="3">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A502DAC0-10A1-4670-A64D-2467E719B3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A35BDB-BB7F-4DB2-BA2B-F7CBAB00651B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1632" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>file</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>brisbanetimes.com.au.130272</t>
+  </si>
+  <si>
+    <t>cnn.167026</t>
   </si>
 </sst>
 </file>
@@ -1339,9 +1342,15 @@
       <c r="B78" t="s">
         <v>9</v>
       </c>
+      <c r="C78" s="3">
+        <v>0.63402777777777775</v>
+      </c>
+      <c r="D78" s="3">
+        <v>0.66319444444444442</v>
+      </c>
       <c r="E78" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.9166666666666674E-2</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -1355,92 +1364,102 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F80" s="3">
+        <f>SUM(E78:E80)</f>
+        <v>2.9166666666666674E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
       <c r="E81" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E82" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E83" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E84" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E85" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E86" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E87" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E88" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E89" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E90" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E91" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E92" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E93" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E94" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E95" s="3">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A35BDB-BB7F-4DB2-BA2B-F7CBAB00651B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA2E79F-2409-4DF1-9E8C-08B1A00E8A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1632" windowWidth="16368" windowHeight="10836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1369,97 +1369,113 @@
         <v>2.9166666666666674E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>25</v>
       </c>
       <c r="B81" t="s">
         <v>9</v>
       </c>
+      <c r="C81" s="3">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="D81" s="3">
+        <v>0.59791666666666665</v>
+      </c>
       <c r="E81" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1.388888888888884E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C82" s="3">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D82" s="3">
+        <v>0.76458333333333328</v>
+      </c>
       <c r="E82" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1.8055555555555491E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E83" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F83" s="3">
+        <f>SUM(E81:E83)</f>
+        <v>3.1944444444444331E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E84" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E85" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E86" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E87" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E88" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E89" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E90" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E91" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E92" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E93" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E94" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E95" s="3">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA2E79F-2409-4DF1-9E8C-08B1A00E8A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06396C8-6CAB-4849-923C-CD7A344C7025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>file</t>
   </si>
@@ -103,6 +103,12 @@
   </si>
   <si>
     <t>cnn.167026</t>
+  </si>
+  <si>
+    <t>cbsnews.146232</t>
+  </si>
+  <si>
+    <t>cbsnews.146237</t>
   </si>
 </sst>
 </file>
@@ -438,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1213,7 +1219,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E67" s="3">
-        <f t="shared" ref="E67:E95" si="1">D67-C67</f>
+        <f t="shared" ref="E67:E122" si="1">D67-C67</f>
         <v>0</v>
       </c>
       <c r="F67" s="3">
@@ -1410,15 +1416,33 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="3">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="D84" s="3">
+        <v>0.54305555555555551</v>
+      </c>
       <c r="E84" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.8749999999999933E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C85" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D85" s="3">
+        <v>0.5541666666666667</v>
+      </c>
       <c r="E85" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.9444444444444198E-3</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -1426,8 +1450,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="F86" s="3">
+        <f>SUM(E84:E86)</f>
+        <v>2.5694444444444353E-2</v>
+      </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>27</v>
+      </c>
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
       <c r="E87" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1477,6 +1511,168 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E95" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E96" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E97" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E98" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E99" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E100" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E101" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E102" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E103" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E104" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E105" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E106" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E107" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E108" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E109" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E110" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E111" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E112" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E113" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E114" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E115" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E116" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E117" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E118" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E119" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E120" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E121" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E122" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06396C8-6CAB-4849-923C-CD7A344C7025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B58D7EE-422D-413B-9883-3A8016D203C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1462,21 +1462,37 @@
       <c r="B87" t="s">
         <v>9</v>
       </c>
+      <c r="C87" s="3">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="D87" s="3">
+        <v>0.47569444444444442</v>
+      </c>
       <c r="E87" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.041666666666663E-2</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C88" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D88" s="3">
+        <v>0.51249999999999996</v>
+      </c>
       <c r="E88" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5555555555555358E-3</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E89" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <f>SUM(E87:E89)</f>
+        <v>1.5972222222222165E-2</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">

--- a/annotators/team/tg/cost_annotation_times.xlsx
+++ b/annotators/team/tg/cost_annotation_times.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B58D7EE-422D-413B-9883-3A8016D203C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3B91DB-AC9C-40F2-BD2A-BA2B4AA12E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>file</t>
   </si>
@@ -109,6 +109,15 @@
   </si>
   <si>
     <t>cbsnews.146237</t>
+  </si>
+  <si>
+    <t>cbsnews.146291</t>
+  </si>
+  <si>
+    <t>cbsnews.146271</t>
+  </si>
+  <si>
+    <t>cbsnews.146310</t>
   </si>
 </sst>
 </file>
@@ -1496,9 +1505,21 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>29</v>
+      </c>
+      <c r="B90" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D90" s="3">
+        <v>0.55763888888888891</v>
+      </c>
       <c r="E90" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5972222222222276E-2</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -1506,11 +1527,27 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="F91" s="3">
+        <f>SUM(E90:E91)</f>
+        <v>1.5972222222222276E-2</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D92" s="3">
+        <v>0.57291666666666663</v>
+      </c>
       <c r="E92" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.819444444444442E-2</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -1518,8 +1555,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="F93" s="3">
+        <f>SUM(E92:E93)</f>
+        <v>3.819444444444442E-2</v>
+      </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>9</v>
+      </c>
       <c r="E94" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
